--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_fewshot_cot.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18139,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26265,7 +26265,7 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27676,7 +27676,7 @@
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27846,7 +27846,7 @@
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -27948,7 +27948,7 @@
       </c>
       <c r="C1619" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28305,7 +28305,7 @@
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28339,7 +28339,7 @@
       </c>
       <c r="C1642" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28781,7 +28781,7 @@
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -28968,7 +28968,7 @@
       </c>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29002,7 +29002,7 @@
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29155,7 +29155,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29223,7 +29223,7 @@
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -30260,7 +30260,7 @@
       </c>
       <c r="C1755" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30362,7 @@
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31025,7 +31025,7 @@
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31144,7 +31144,7 @@
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31450,7 +31450,7 @@
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31552,7 +31552,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31637,7 +31637,7 @@
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31807,7 +31807,7 @@
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32011,7 +32011,7 @@
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32793,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33099,7 +33099,7 @@
       </c>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -33116,7 +33116,7 @@
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
       </c>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="C1964" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34068,7 +34068,7 @@
       </c>
       <c r="C1979" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="C2083" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35938,7 +35938,7 @@
       </c>
       <c r="C2089" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35989,7 @@
       </c>
       <c r="C2092" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="C2096" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36142,7 +36142,7 @@
       </c>
       <c r="C2101" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36159,7 +36159,7 @@
       </c>
       <c r="C2102" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36329,7 +36329,7 @@
       </c>
       <c r="C2112" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="C2131" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36754,7 +36754,7 @@
       </c>
       <c r="C2137" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36788,7 +36788,7 @@
       </c>
       <c r="C2139" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="C2162" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37281,7 +37281,7 @@
       </c>
       <c r="C2168" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37638,7 +37638,7 @@
       </c>
       <c r="C2189" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="C2197" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37927,7 +37927,7 @@
       </c>
       <c r="C2206" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38080,7 +38080,7 @@
       </c>
       <c r="C2215" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38318,7 +38318,7 @@
       </c>
       <c r="C2229" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
       </c>
       <c r="C2232" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38386,7 +38386,7 @@
       </c>
       <c r="C2233" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38420,7 +38420,7 @@
       </c>
       <c r="C2235" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38437,7 +38437,7 @@
       </c>
       <c r="C2236" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38454,7 +38454,7 @@
       </c>
       <c r="C2237" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="C2252" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38777,7 +38777,7 @@
       </c>
       <c r="C2256" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C2359" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40698,7 +40698,7 @@
       </c>
       <c r="C2369" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -41072,7 +41072,7 @@
       </c>
       <c r="C2391" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41446,7 +41446,7 @@
       </c>
       <c r="C2413" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41582,7 +41582,7 @@
       </c>
       <c r="C2421" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="C2425" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41888,7 +41888,7 @@
       </c>
       <c r="C2439" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41956,7 +41956,7 @@
       </c>
       <c r="C2443" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="C2445" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="C2458" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="C2479" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43214,7 +43214,7 @@
       </c>
       <c r="C2517" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43316,7 +43316,7 @@
       </c>
       <c r="C2523" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="C2529" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="C2531" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43588,7 +43588,7 @@
       </c>
       <c r="C2539" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="C2549" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="C2557" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43945,7 +43945,7 @@
       </c>
       <c r="C2560" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44047,7 +44047,7 @@
       </c>
       <c r="C2566" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44132,7 +44132,7 @@
       </c>
       <c r="C2571" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="C2572" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44251,7 +44251,7 @@
       </c>
       <c r="C2578" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44438,7 +44438,7 @@
       </c>
       <c r="C2589" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44591,7 +44591,7 @@
       </c>
       <c r="C2598" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C2601" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44846,7 +44846,7 @@
       </c>
       <c r="C2613" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="C2620" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45050,7 +45050,7 @@
       </c>
       <c r="C2625" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45152,7 +45152,7 @@
       </c>
       <c r="C2631" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45424,7 +45424,7 @@
       </c>
       <c r="C2647" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="C2688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46444,7 +46444,7 @@
       </c>
       <c r="C2707" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="C2715" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46818,7 +46818,7 @@
       </c>
       <c r="C2729" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -46903,7 +46903,7 @@
       </c>
       <c r="C2734" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="C2737" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47022,7 +47022,7 @@
       </c>
       <c r="C2741" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47311,7 +47311,7 @@
       </c>
       <c r="C2758" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47481,7 +47481,7 @@
       </c>
       <c r="C2768" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47583,7 +47583,7 @@
       </c>
       <c r="C2774" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47838,7 +47838,7 @@
       </c>
       <c r="C2789" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48212,7 +48212,7 @@
       </c>
       <c r="C2811" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48314,7 +48314,7 @@
       </c>
       <c r="C2817" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48348,7 +48348,7 @@
       </c>
       <c r="C2819" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48416,7 +48416,7 @@
       </c>
       <c r="C2823" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48722,7 +48722,7 @@
       </c>
       <c r="C2841" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48739,7 @@
       </c>
       <c r="C2842" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48756,7 +48756,7 @@
       </c>
       <c r="C2843" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48926,7 +48926,7 @@
       </c>
       <c r="C2853" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49028,7 +49028,7 @@
       </c>
       <c r="C2859" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49606,7 +49606,7 @@
       </c>
       <c r="C2893" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="C2898" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49997,7 +49997,7 @@
       </c>
       <c r="C2916" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="C2923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="C2958" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="C2970" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51034,7 +51034,7 @@
       </c>
       <c r="C2977" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51187,7 +51187,7 @@
       </c>
       <c r="C2986" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="C2992" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="C2997" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.86</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7591308018190779</v>
+        <v>0.7675235022328862</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8622843404534325</v>
+        <v>0.8715051437657779</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7530690200681189</v>
+        <v>0.7637063975363444</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7712060126774639</v>
+        <v>0.7810350468337032</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>671.1463453010001</v>
+        <v>1540.478427227004</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2237154484336667</v>
+        <v>0.5134928090756682</v>
       </c>
     </row>
   </sheetData>
